--- a/SourceFiles/Data/ProspectData.xlsx
+++ b/SourceFiles/Data/ProspectData.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,14 +16,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +48,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,153 +429,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC104"/>
+  <dimension ref="A1:AG104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Candidate Id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Mobile number</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Family income</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Current Status</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Email id</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Preferred job type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Preferred job timing</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Address PIN</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Smart Device</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Have internet access</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Preferred language</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Aadhar number</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Family profession</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Health Issues</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Past work exp</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Past sector</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Family support</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Members in family</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Smoking habits</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Drinking habits</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Reference mobile no</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Source of info</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Insta id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Previous job dropped</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Reason for drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Plan study further</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed_31</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed_32</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed_33</t>
         </is>
       </c>
     </row>
@@ -687,6 +723,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Counselling</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="AG2" s="2" t="n">
+        <v>46024</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -816,6 +864,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="AG3" s="2" t="n">
+        <v>46044</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -945,6 +1005,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Counselling</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" s="2" t="n">
+        <v>45872</v>
+      </c>
+      <c r="AG4" s="2" t="n">
+        <v>46041</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1146,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="AG5" s="2" t="n">
+        <v>45971</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1203,6 +1287,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="AG6" s="2" t="n">
+        <v>46045</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1424,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="AG7" s="2" t="n">
+        <v>45941</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1457,6 +1565,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Counselling</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" s="2" t="n">
+        <v>45898</v>
+      </c>
+      <c r="AG8" s="2" t="n">
+        <v>45918</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1586,6 +1706,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="AG9" s="2" t="n">
+        <v>45998</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1715,6 +1847,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="AG10" s="2" t="n">
+        <v>45989</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1844,6 +1988,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" s="2" t="n">
+        <v>45928</v>
+      </c>
+      <c r="AG11" s="2" t="n">
+        <v>45978</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1973,6 +2129,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="AG12" s="2" t="n">
+        <v>46032</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2102,6 +2270,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="AG13" s="2" t="n">
+        <v>45989</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2231,6 +2411,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" s="2" t="n">
+        <v>46047</v>
+      </c>
+      <c r="AG14" s="2" t="n">
+        <v>46051</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2356,6 +2548,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="AG15" s="2" t="n">
+        <v>46050</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2485,6 +2689,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="AG16" s="2" t="n">
+        <v>46025</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2614,6 +2830,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="AG17" s="2" t="n">
+        <v>46046</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2739,6 +2967,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="AG18" s="2" t="n">
+        <v>46035</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2864,6 +3104,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="AG19" s="2" t="n">
+        <v>46033</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2989,6 +3241,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="AG20" s="2" t="n">
+        <v>45974</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3114,6 +3378,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Counselling</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="AG21" s="2" t="n">
+        <v>46037</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3239,6 +3515,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="AG22" s="2" t="n">
+        <v>46050</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3368,6 +3656,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" s="2" t="n">
+        <v>45934</v>
+      </c>
+      <c r="AG23" s="2" t="n">
+        <v>45948</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3497,6 +3797,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="AG24" s="2" t="n">
+        <v>46037</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3622,6 +3934,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" s="2" t="n">
+        <v>45983</v>
+      </c>
+      <c r="AG25" s="2" t="n">
+        <v>46042</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3751,6 +4075,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" s="2" t="n">
+        <v>45886</v>
+      </c>
+      <c r="AG26" s="2" t="n">
+        <v>45982</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3880,6 +4216,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Counselling</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" s="2" t="n">
+        <v>45914</v>
+      </c>
+      <c r="AG27" s="2" t="n">
+        <v>46032</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4009,6 +4357,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="AG28" s="2" t="n">
+        <v>46049</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4138,6 +4498,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AG29" s="2" t="n">
+        <v>46030</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4267,6 +4639,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Counselling</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="AG30" s="2" t="n">
+        <v>46021</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4396,6 +4780,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" s="2" t="n">
+        <v>45969</v>
+      </c>
+      <c r="AG31" s="2" t="n">
+        <v>46032</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4525,6 +4921,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" s="2" t="n">
+        <v>45885</v>
+      </c>
+      <c r="AG32" s="2" t="n">
+        <v>45897</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4654,6 +5062,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" s="2" t="n">
+        <v>45984</v>
+      </c>
+      <c r="AG33" s="2" t="n">
+        <v>46047</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4783,6 +5203,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" s="2" t="n">
+        <v>45871</v>
+      </c>
+      <c r="AG34" s="2" t="n">
+        <v>45885</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4912,6 +5344,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" s="2" t="n">
+        <v>45963</v>
+      </c>
+      <c r="AG35" s="2" t="n">
+        <v>46004</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5041,6 +5485,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" s="2" t="n">
+        <v>45956</v>
+      </c>
+      <c r="AG36" s="2" t="n">
+        <v>46034</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5170,6 +5626,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" s="2" t="n">
+        <v>45892</v>
+      </c>
+      <c r="AG37" s="2" t="n">
+        <v>46031</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5299,6 +5767,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="AG38" s="2" t="n">
+        <v>46026</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5428,6 +5908,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" s="2" t="n">
+        <v>45935</v>
+      </c>
+      <c r="AG39" s="2" t="n">
+        <v>46006</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5557,6 +6049,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="AG40" s="2" t="n">
+        <v>46023</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5686,6 +6190,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="AG41" s="2" t="n">
+        <v>46045</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5811,6 +6327,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>Counselling</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" s="2" t="n">
+        <v>45885</v>
+      </c>
+      <c r="AG42" s="2" t="n">
+        <v>45942</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5936,6 +6464,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="AG43" s="2" t="n">
+        <v>45998</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6065,6 +6605,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="AG44" s="2" t="n">
+        <v>46046</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6194,6 +6746,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>Counselling</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="AG45" s="2" t="n">
+        <v>46015</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6323,6 +6887,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>Counselling</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="AG46" s="2" t="n">
+        <v>45972</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6448,6 +7024,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" s="2" t="n">
+        <v>46011</v>
+      </c>
+      <c r="AG47" s="2" t="n">
+        <v>46042</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6577,6 +7165,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" s="2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="AG48" s="2" t="n">
+        <v>45966</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6706,6 +7306,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>Counselling</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="AG49" s="2" t="n">
+        <v>46011</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6835,6 +7447,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="AG50" s="2" t="n">
+        <v>46044</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6960,6 +7584,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" s="2" t="n">
+        <v>45893</v>
+      </c>
+      <c r="AG51" s="2" t="n">
+        <v>45932</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7085,6 +7721,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="AG52" s="2" t="n">
+        <v>46025</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7214,6 +7862,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="AG53" s="2" t="n">
+        <v>45989</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7343,6 +8003,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" s="2" t="n">
+        <v>45970</v>
+      </c>
+      <c r="AG54" s="2" t="n">
+        <v>45984</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7472,6 +8144,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="AG55" s="2" t="n">
+        <v>46045</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7597,6 +8281,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="AG56" s="2" t="n">
+        <v>46013</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7722,6 +8418,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>Counselling</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="AG57" s="2" t="n">
+        <v>45916</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7851,6 +8559,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" s="2" t="n">
+        <v>45916</v>
+      </c>
+      <c r="AG58" s="2" t="n">
+        <v>45930</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7980,6 +8700,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" s="2" t="n">
+        <v>45956</v>
+      </c>
+      <c r="AG59" s="2" t="n">
+        <v>45996</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8109,6 +8841,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>Counselling</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="AG60" s="2" t="n">
+        <v>45987</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8238,6 +8982,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" s="2" t="n">
+        <v>45923</v>
+      </c>
+      <c r="AG61" s="2" t="n">
+        <v>46006</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8367,6 +9123,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" s="2" t="n">
+        <v>45948</v>
+      </c>
+      <c r="AG62" s="2" t="n">
+        <v>45997</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8492,6 +9260,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>Counselling</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="AG63" s="2" t="n">
+        <v>45992</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8621,6 +9401,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" s="2" t="n">
+        <v>46005</v>
+      </c>
+      <c r="AG64" s="2" t="n">
+        <v>46019</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8750,6 +9542,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="AG65" s="2" t="n">
+        <v>45988</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8879,6 +9683,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="AG66" s="2" t="n">
+        <v>46018</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9008,6 +9824,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>Counselling</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" s="2" t="n">
+        <v>46046</v>
+      </c>
+      <c r="AG67" s="2" t="n">
+        <v>46047</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9133,6 +9961,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="AG68" s="2" t="n">
+        <v>46030</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9262,6 +10102,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="AG69" s="2" t="n">
+        <v>46011</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9387,6 +10239,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="AG70" s="2" t="n">
+        <v>46025</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9516,6 +10380,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="AG71" s="2" t="n">
+        <v>46049</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9645,6 +10521,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>Counselling</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" s="2" t="n">
+        <v>45934</v>
+      </c>
+      <c r="AG72" s="2" t="n">
+        <v>45991</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9774,6 +10662,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="AG73" s="2" t="n">
+        <v>46028</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9903,6 +10803,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="AG74" s="2" t="n">
+        <v>45995</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -10032,6 +10944,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" s="2" t="n">
+        <v>45920</v>
+      </c>
+      <c r="AG75" s="2" t="n">
+        <v>46031</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -10157,6 +11081,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" s="2" t="n">
+        <v>45885</v>
+      </c>
+      <c r="AG76" s="2" t="n">
+        <v>45979</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10282,6 +11218,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="AG77" s="2" t="n">
+        <v>46050</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10411,6 +11359,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="AG78" s="2" t="n">
+        <v>46015</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10540,6 +11500,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="AG79" s="2" t="n">
+        <v>46004</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10669,6 +11641,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" s="2" t="n">
+        <v>46026</v>
+      </c>
+      <c r="AG80" s="2" t="n">
+        <v>46033</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10794,6 +11778,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="AG81" s="2" t="n">
+        <v>46051</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10919,6 +11915,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="AG82" s="2" t="n">
+        <v>46025</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11048,6 +12056,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr"/>
+      <c r="AF83" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="AG83" s="2" t="n">
+        <v>45946</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -11173,6 +12193,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr"/>
+      <c r="AF84" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="AG84" s="2" t="n">
+        <v>46024</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -11302,6 +12334,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr"/>
+      <c r="AF85" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="AG85" s="2" t="n">
+        <v>45992</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -11431,6 +12475,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr"/>
+      <c r="AF86" s="2" t="n">
+        <v>45949</v>
+      </c>
+      <c r="AG86" s="2" t="n">
+        <v>46045</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11560,6 +12616,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr"/>
+      <c r="AF87" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="AG87" s="2" t="n">
+        <v>45911</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11689,6 +12757,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr"/>
+      <c r="AF88" s="2" t="n">
+        <v>46046</v>
+      </c>
+      <c r="AG88" s="2" t="n">
+        <v>46051</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11818,6 +12898,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr"/>
+      <c r="AF89" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="AG89" s="2" t="n">
+        <v>45966</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11943,6 +13035,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr"/>
+      <c r="AF90" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="AG90" s="2" t="n">
+        <v>46022</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -12068,6 +13172,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr"/>
+      <c r="AF91" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="AG91" s="2" t="n">
+        <v>45966</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -12197,6 +13313,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr"/>
+      <c r="AF92" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="AG92" s="2" t="n">
+        <v>45994</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -12326,6 +13454,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr"/>
+      <c r="AF93" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="AG93" s="2" t="n">
+        <v>45965</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -12455,6 +13595,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr"/>
+      <c r="AF94" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="AG94" s="2" t="n">
+        <v>46035</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12584,6 +13736,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr"/>
+      <c r="AF95" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="AG95" s="2" t="n">
+        <v>45991</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -12713,6 +13877,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr"/>
+      <c r="AF96" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="AG96" s="2" t="n">
+        <v>45947</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -12838,6 +14014,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr"/>
+      <c r="AF97" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="AG97" s="2" t="n">
+        <v>46021</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12967,6 +14155,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr"/>
+      <c r="AF98" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="AG98" s="2" t="n">
+        <v>46030</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -13096,6 +14296,18 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr"/>
+      <c r="AF99" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="AG99" s="2" t="n">
+        <v>45943</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -13225,6 +14437,18 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr"/>
+      <c r="AF100" s="2" t="n">
+        <v>45872</v>
+      </c>
+      <c r="AG100" s="2" t="n">
+        <v>45927</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -13349,6 +14573,18 @@
         <is>
           <t>Yes</t>
         </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr"/>
+      <c r="AF101" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AG101" s="2" t="n">
+        <v>46040</v>
       </c>
     </row>
     <row r="102">
@@ -13427,6 +14663,18 @@
       <c r="AA102" t="inlineStr"/>
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr"/>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>identification</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr"/>
+      <c r="AF102" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="AG102" s="2" t="n">
+        <v>46045</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -13504,32 +14752,36 @@
       <c r="AA103" t="inlineStr"/>
       <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="inlineStr"/>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>Ready for training</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr"/>
+      <c r="AF103" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="AG103" s="2" t="n">
+        <v>46031</v>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="A104" t="n">
+        <v>103</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Amit</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>127544335</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>120000</t>
-        </is>
+      <c r="C104" t="n">
+        <v>127544335</v>
+      </c>
+      <c r="D104" t="n">
+        <v>20</v>
+      </c>
+      <c r="E104" t="n">
+        <v>120000</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13556,10 +14808,8 @@
           <t>No Preference</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
+      <c r="K104" t="n">
+        <v>1234</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -13591,6 +14841,18 @@
       <c r="AA104" t="inlineStr"/>
       <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr"/>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr"/>
+      <c r="AF104" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="AG104" s="2" t="n">
+        <v>46026</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
